--- a/product_selector_out/STM32H723-733 - diff.xlsx
+++ b/product_selector_out/STM32H723-733 - diff.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
